--- a/results_OV3heads_mmdec_pixeldec__head_1xA6000_12_8M_epoch20_lr_1e-5_weight_1_scheduler_timescale_3000.xlsx
+++ b/results_OV3heads_mmdec_pixeldec__head_1xA6000_12_8M_epoch20_lr_1e-5_weight_1_scheduler_timescale_3000.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E4"/>
+  <dimension ref="A1:E7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -506,6 +506,69 @@
         <v>75.66000366210938</v>
       </c>
     </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>SAM3</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>PotsdamDataset</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>75.19999694824219</v>
+      </c>
+      <c r="D5" t="n">
+        <v>56.31999969482422</v>
+      </c>
+      <c r="E5" t="n">
+        <v>70.40000152587891</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>SAM3</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>LoveDADataset</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>60.59000015258789</v>
+      </c>
+      <c r="D6" t="n">
+        <v>45.43999862670898</v>
+      </c>
+      <c r="E6" t="n">
+        <v>63.02000045776367</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>SAM3</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>iSAIDDataset</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>95.80000305175781</v>
+      </c>
+      <c r="D7" t="n">
+        <v>26.04999923706055</v>
+      </c>
+      <c r="E7" t="n">
+        <v>45.47000122070312</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
